--- a/frontend/assets/Files/e3-exp.xlsx
+++ b/frontend/assets/Files/e3-exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4692AA6E-AA5F-41F6-A8D1-046C0894977C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4850368E-2E54-4888-972E-97265EDDF151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{E9B7B421-50BE-4275-91F8-A057181DCB3A}"/>
   </bookViews>
@@ -447,6 +447,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -561,7 +564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -569,34 +572,38 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -937,8 +944,9 @@
   <sheetFormatPr defaultColWidth="42.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.6640625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -954,7 +962,7 @@
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
@@ -962,16 +970,16 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
-        <v>46189</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="12">
+        <v>45824</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="10" t="s">
         <v>6</v>
       </c>
     </row>
@@ -979,16 +987,16 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
-        <v>46189</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="12">
+        <v>45824</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="10" t="s">
         <v>9</v>
       </c>
     </row>
@@ -996,16 +1004,16 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
-        <v>46189</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="12">
+        <v>45824</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1013,16 +1021,16 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
-        <v>46189</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="12">
+        <v>45824</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1030,16 +1038,16 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
-        <v>46189</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="12">
+        <v>45824</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1047,16 +1055,16 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
-        <v>46189</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="12">
+        <v>45824</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1064,16 +1072,16 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
-        <v>46200</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="12">
+        <v>45835</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="10" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1081,16 +1089,16 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
-        <v>46204</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="12">
+        <v>45839</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="10" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1098,16 +1106,16 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
-        <v>46204</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="12">
+        <v>45839</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="10" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1115,16 +1123,16 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
-        <v>46204</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="12">
+        <v>45839</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1132,16 +1140,16 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
-        <v>46221</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="12">
+        <v>45856</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1149,16 +1157,16 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
-        <v>46204</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="12">
+        <v>45839</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1166,16 +1174,16 @@
       <c r="A14">
         <v>22</v>
       </c>
-      <c r="B14" s="3">
-        <v>46228</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="B14" s="12">
+        <v>45863</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1183,16 +1191,16 @@
       <c r="A15">
         <v>23</v>
       </c>
-      <c r="B15" s="3">
-        <v>46226</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="B15" s="12">
+        <v>45861</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="10" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1200,16 +1208,16 @@
       <c r="A16">
         <v>24</v>
       </c>
-      <c r="B16" s="3">
-        <v>46229</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="12">
+        <v>45864</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="10" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1217,16 +1225,16 @@
       <c r="A17">
         <v>25</v>
       </c>
-      <c r="B17" s="3">
-        <v>46230</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="12">
+        <v>45865</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="10" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1234,16 +1242,16 @@
       <c r="A18">
         <v>26</v>
       </c>
-      <c r="B18" s="3">
-        <v>46232</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="12">
+        <v>45867</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="10" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1251,16 +1259,16 @@
       <c r="A19">
         <v>27</v>
       </c>
-      <c r="B19" s="3">
-        <v>46229</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="B19" s="12">
+        <v>45864</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="10" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1268,16 +1276,16 @@
       <c r="A20">
         <v>28</v>
       </c>
-      <c r="B20" s="3">
-        <v>46230</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="12">
+        <v>45865</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="10" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1285,16 +1293,16 @@
       <c r="A21">
         <v>29</v>
       </c>
-      <c r="B21" s="3">
-        <v>46233</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="B21" s="12">
+        <v>45868</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1302,16 +1310,16 @@
       <c r="A22">
         <v>30</v>
       </c>
-      <c r="B22" s="3">
-        <v>46234</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="B22" s="12">
+        <v>45869</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1319,16 +1327,16 @@
       <c r="A23">
         <v>31</v>
       </c>
-      <c r="B23" s="3">
-        <v>46223</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="B23" s="12">
+        <v>45858</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1336,16 +1344,16 @@
       <c r="A24">
         <v>32</v>
       </c>
-      <c r="B24" s="3">
-        <v>46234</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="B24" s="12">
+        <v>45869</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1353,14 +1361,14 @@
       <c r="A25">
         <v>40</v>
       </c>
-      <c r="B25" s="3">
-        <v>46236</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="B25" s="12">
+        <v>45871</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="6" t="s">
+      <c r="D25" s="3"/>
+      <c r="E25" s="10" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1368,14 +1376,14 @@
       <c r="A26">
         <v>41</v>
       </c>
-      <c r="B26" s="3">
-        <v>46238</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="B26" s="12">
+        <v>45873</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="6" t="s">
+      <c r="D26" s="3"/>
+      <c r="E26" s="10" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1383,14 +1391,14 @@
       <c r="A27">
         <v>42</v>
       </c>
-      <c r="B27" s="3">
-        <v>46240</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="B27" s="12">
+        <v>45875</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="6" t="s">
+      <c r="D27" s="3"/>
+      <c r="E27" s="10" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1398,14 +1406,14 @@
       <c r="A28">
         <v>43</v>
       </c>
-      <c r="B28" s="3">
-        <v>46240</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="B28" s="12">
+        <v>45875</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="6" t="s">
+      <c r="D28" s="3"/>
+      <c r="E28" s="10" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1413,14 +1421,14 @@
       <c r="A29">
         <v>44</v>
       </c>
-      <c r="B29" s="3">
-        <v>46239</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="B29" s="12">
+        <v>45874</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="6" t="s">
+      <c r="D29" s="3"/>
+      <c r="E29" s="10" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1428,14 +1436,14 @@
       <c r="A30">
         <v>45</v>
       </c>
-      <c r="B30" s="3">
-        <v>46241</v>
-      </c>
-      <c r="C30" s="5" t="s">
+      <c r="B30" s="12">
+        <v>45876</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="6" t="s">
+      <c r="D30" s="3"/>
+      <c r="E30" s="10" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1443,14 +1451,14 @@
       <c r="A31">
         <v>46</v>
       </c>
-      <c r="B31" s="3">
-        <v>46244</v>
-      </c>
-      <c r="C31" s="5" t="s">
+      <c r="B31" s="12">
+        <v>45879</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="6" t="s">
+      <c r="D31" s="3"/>
+      <c r="E31" s="10" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1458,14 +1466,14 @@
       <c r="A32">
         <v>47</v>
       </c>
-      <c r="B32" s="3">
-        <v>46252</v>
-      </c>
-      <c r="C32" s="5" t="s">
+      <c r="B32" s="12">
+        <v>45887</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="6" t="s">
+      <c r="D32" s="3"/>
+      <c r="E32" s="10" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1473,14 +1481,14 @@
       <c r="A33">
         <v>48</v>
       </c>
-      <c r="B33" s="3">
-        <v>46259</v>
-      </c>
-      <c r="C33" s="5" t="s">
+      <c r="B33" s="12">
+        <v>45894</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="6" t="s">
+      <c r="D33" s="3"/>
+      <c r="E33" s="10" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1488,14 +1496,14 @@
       <c r="A34">
         <v>49</v>
       </c>
-      <c r="B34" s="3">
-        <v>46264</v>
-      </c>
-      <c r="C34" s="5" t="s">
+      <c r="B34" s="12">
+        <v>45899</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="6" t="s">
+      <c r="D34" s="3"/>
+      <c r="E34" s="10" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1503,16 +1511,16 @@
       <c r="A35">
         <v>50</v>
       </c>
-      <c r="B35" s="3">
-        <v>46264</v>
-      </c>
-      <c r="C35" s="5" t="s">
+      <c r="B35" s="12">
+        <v>45899</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="10" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1520,14 +1528,14 @@
       <c r="A36">
         <v>52</v>
       </c>
-      <c r="B36" s="3">
-        <v>46246</v>
-      </c>
-      <c r="C36" s="9" t="s">
+      <c r="B36" s="12">
+        <v>45881</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="6" t="s">
+      <c r="D36" s="3"/>
+      <c r="E36" s="10" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1535,14 +1543,14 @@
       <c r="A37">
         <v>55</v>
       </c>
-      <c r="B37" s="3">
-        <v>46275</v>
-      </c>
-      <c r="C37" s="5" t="s">
+      <c r="B37" s="12">
+        <v>45910</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="6" t="s">
+      <c r="D37" s="3"/>
+      <c r="E37" s="10" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1550,14 +1558,14 @@
       <c r="A38">
         <v>56</v>
       </c>
-      <c r="B38" s="3">
-        <v>46277</v>
-      </c>
-      <c r="C38" s="5" t="s">
+      <c r="B38" s="12">
+        <v>45912</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="6" t="s">
+      <c r="D38" s="3"/>
+      <c r="E38" s="10" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1565,14 +1573,14 @@
       <c r="A39">
         <v>57</v>
       </c>
-      <c r="B39" s="3">
-        <v>46281</v>
-      </c>
-      <c r="C39" s="5" t="s">
+      <c r="B39" s="12">
+        <v>45916</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="6" t="s">
+      <c r="D39" s="3"/>
+      <c r="E39" s="10" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1580,14 +1588,14 @@
       <c r="A40">
         <v>58</v>
       </c>
-      <c r="B40" s="3">
-        <v>46277</v>
-      </c>
-      <c r="C40" s="5" t="s">
+      <c r="B40" s="12">
+        <v>45912</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="6" t="s">
+      <c r="D40" s="3"/>
+      <c r="E40" s="10" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1595,14 +1603,14 @@
       <c r="A41">
         <v>59</v>
       </c>
-      <c r="B41" s="3">
-        <v>46278</v>
-      </c>
-      <c r="C41" s="5" t="s">
+      <c r="B41" s="12">
+        <v>45913</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="6" t="s">
+      <c r="D41" s="3"/>
+      <c r="E41" s="10" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1610,14 +1618,14 @@
       <c r="A42">
         <v>60</v>
       </c>
-      <c r="B42" s="3">
-        <v>46279</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="B42" s="12">
+        <v>45914</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="6" t="s">
+      <c r="D42" s="3"/>
+      <c r="E42" s="10" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1625,14 +1633,14 @@
       <c r="A43">
         <v>61</v>
       </c>
-      <c r="B43" s="3">
-        <v>46279</v>
-      </c>
-      <c r="C43" s="5" t="s">
+      <c r="B43" s="12">
+        <v>45914</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="6" t="s">
+      <c r="D43" s="3"/>
+      <c r="E43" s="10" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1640,14 +1648,14 @@
       <c r="A44">
         <v>62</v>
       </c>
-      <c r="B44" s="3">
-        <v>46280</v>
-      </c>
-      <c r="C44" s="5" t="s">
+      <c r="B44" s="12">
+        <v>45915</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="6" t="s">
+      <c r="D44" s="3"/>
+      <c r="E44" s="10" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1655,14 +1663,14 @@
       <c r="A45">
         <v>63</v>
       </c>
-      <c r="B45" s="3">
-        <v>46283</v>
-      </c>
-      <c r="C45" s="5" t="s">
+      <c r="B45" s="12">
+        <v>45918</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="6" t="s">
+      <c r="D45" s="3"/>
+      <c r="E45" s="10" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1670,14 +1678,14 @@
       <c r="A46">
         <v>64</v>
       </c>
-      <c r="B46" s="3">
-        <v>46283</v>
-      </c>
-      <c r="C46" s="5" t="s">
+      <c r="B46" s="12">
+        <v>45918</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="6" t="s">
+      <c r="D46" s="3"/>
+      <c r="E46" s="10" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1685,14 +1693,14 @@
       <c r="A47">
         <v>65</v>
       </c>
-      <c r="B47" s="3">
-        <v>46283</v>
-      </c>
-      <c r="C47" s="5" t="s">
+      <c r="B47" s="12">
+        <v>45918</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D47" s="4"/>
-      <c r="E47" s="6" t="s">
+      <c r="D47" s="3"/>
+      <c r="E47" s="10" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1700,14 +1708,14 @@
       <c r="A48">
         <v>66</v>
       </c>
-      <c r="B48" s="3">
-        <v>46284</v>
-      </c>
-      <c r="C48" s="5" t="s">
+      <c r="B48" s="12">
+        <v>45919</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D48" s="4"/>
-      <c r="E48" s="6" t="s">
+      <c r="D48" s="3"/>
+      <c r="E48" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1715,14 +1723,14 @@
       <c r="A49">
         <v>67</v>
       </c>
-      <c r="B49" s="3">
-        <v>46275</v>
-      </c>
-      <c r="C49" s="5" t="s">
+      <c r="B49" s="12">
+        <v>45910</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="4"/>
-      <c r="E49" s="6" t="s">
+      <c r="D49" s="3"/>
+      <c r="E49" s="10" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1730,14 +1738,14 @@
       <c r="A50">
         <v>68</v>
       </c>
-      <c r="B50" s="3">
-        <v>46285</v>
-      </c>
-      <c r="C50" s="5" t="s">
+      <c r="B50" s="12">
+        <v>45920</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="6" t="s">
+      <c r="D50" s="3"/>
+      <c r="E50" s="10" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1745,14 +1753,14 @@
       <c r="A51">
         <v>69</v>
       </c>
-      <c r="B51" s="3">
-        <v>46287</v>
-      </c>
-      <c r="C51" s="5" t="s">
+      <c r="B51" s="12">
+        <v>45922</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="4"/>
-      <c r="E51" s="6" t="s">
+      <c r="D51" s="3"/>
+      <c r="E51" s="10" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1760,14 +1768,14 @@
       <c r="A52">
         <v>70</v>
       </c>
-      <c r="B52" s="3">
-        <v>46289</v>
-      </c>
-      <c r="C52" s="5" t="s">
+      <c r="B52" s="12">
+        <v>45924</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D52" s="4"/>
-      <c r="E52" s="6" t="s">
+      <c r="D52" s="3"/>
+      <c r="E52" s="10" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1775,14 +1783,14 @@
       <c r="A53">
         <v>71</v>
       </c>
-      <c r="B53" s="3">
-        <v>46290</v>
-      </c>
-      <c r="C53" s="5" t="s">
+      <c r="B53" s="12">
+        <v>45925</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D53" s="4"/>
-      <c r="E53" s="6" t="s">
+      <c r="D53" s="3"/>
+      <c r="E53" s="10" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1790,14 +1798,14 @@
       <c r="A54">
         <v>72</v>
       </c>
-      <c r="B54" s="3">
-        <v>46289</v>
-      </c>
-      <c r="C54" s="5" t="s">
+      <c r="B54" s="12">
+        <v>45924</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D54" s="4"/>
-      <c r="E54" s="6" t="s">
+      <c r="D54" s="3"/>
+      <c r="E54" s="10" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1805,14 +1813,14 @@
       <c r="A55">
         <v>73</v>
       </c>
-      <c r="B55" s="3">
-        <v>46290</v>
-      </c>
-      <c r="C55" s="5" t="s">
+      <c r="B55" s="12">
+        <v>45925</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D55" s="4"/>
-      <c r="E55" s="6" t="s">
+      <c r="D55" s="3"/>
+      <c r="E55" s="10" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1820,14 +1828,14 @@
       <c r="A56">
         <v>74</v>
       </c>
-      <c r="B56" s="3">
-        <v>46292</v>
-      </c>
-      <c r="C56" s="5" t="s">
+      <c r="B56" s="12">
+        <v>45927</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D56" s="4"/>
-      <c r="E56" s="6" t="s">
+      <c r="D56" s="3"/>
+      <c r="E56" s="10" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1835,14 +1843,14 @@
       <c r="A57">
         <v>77</v>
       </c>
-      <c r="B57" s="3">
-        <v>46293</v>
-      </c>
-      <c r="C57" s="5" t="s">
+      <c r="B57" s="12">
+        <v>45928</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="6" t="s">
+      <c r="D57" s="3"/>
+      <c r="E57" s="10" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1850,14 +1858,14 @@
       <c r="A58">
         <v>78</v>
       </c>
-      <c r="B58" s="7"/>
-      <c r="C58" s="5" t="s">
+      <c r="B58" s="13"/>
+      <c r="C58" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E58" s="10" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1865,16 +1873,16 @@
       <c r="A59">
         <v>79</v>
       </c>
-      <c r="B59" s="3">
-        <v>46297</v>
-      </c>
-      <c r="C59" s="5" t="s">
+      <c r="B59" s="12">
+        <v>45932</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D59" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="10" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1882,16 +1890,16 @@
       <c r="A60">
         <v>80</v>
       </c>
-      <c r="B60" s="3">
-        <v>46298</v>
-      </c>
-      <c r="C60" s="5" t="s">
+      <c r="B60" s="12">
+        <v>45933</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E60" s="10" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1899,16 +1907,16 @@
       <c r="A61">
         <v>81</v>
       </c>
-      <c r="B61" s="3">
-        <v>46299</v>
-      </c>
-      <c r="C61" s="5" t="s">
+      <c r="B61" s="12">
+        <v>45934</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="D61" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E61" s="10" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1916,16 +1924,16 @@
       <c r="A62">
         <v>82</v>
       </c>
-      <c r="B62" s="3">
-        <v>46301</v>
-      </c>
-      <c r="C62" s="5" t="s">
+      <c r="B62" s="12">
+        <v>45936</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D62" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E62" s="6" t="s">
+      <c r="E62" s="10" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1933,33 +1941,33 @@
       <c r="A63">
         <v>83</v>
       </c>
-      <c r="B63" s="3">
-        <v>46308</v>
-      </c>
-      <c r="C63" s="5" t="s">
+      <c r="B63" s="12">
+        <v>45943</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>84</v>
       </c>
-      <c r="B64" s="3">
-        <v>46304</v>
-      </c>
-      <c r="C64" s="5" t="s">
+      <c r="B64" s="12">
+        <v>45939</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E64" s="6" t="s">
+      <c r="E64" s="10" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1967,16 +1975,16 @@
       <c r="A65">
         <v>85</v>
       </c>
-      <c r="B65" s="3">
-        <v>46313</v>
-      </c>
-      <c r="C65" s="5" t="s">
+      <c r="B65" s="12">
+        <v>45948</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="D65" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" s="10" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1984,14 +1992,14 @@
       <c r="A66">
         <v>86</v>
       </c>
-      <c r="B66" s="3">
-        <v>46299</v>
-      </c>
-      <c r="C66" s="5" t="s">
+      <c r="B66" s="12">
+        <v>45934</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D66" s="4"/>
-      <c r="E66" s="6" t="s">
+      <c r="D66" s="3"/>
+      <c r="E66" s="10" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1999,16 +2007,16 @@
       <c r="A67">
         <v>87</v>
       </c>
-      <c r="B67" s="3">
-        <v>46314</v>
-      </c>
-      <c r="C67" s="5" t="s">
+      <c r="B67" s="12">
+        <v>45949</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D67" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="E67" s="10" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2016,16 +2024,16 @@
       <c r="A68">
         <v>88</v>
       </c>
-      <c r="B68" s="3">
-        <v>46314</v>
-      </c>
-      <c r="C68" s="5" t="s">
+      <c r="B68" s="12">
+        <v>45949</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="D68" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E68" s="6" t="s">
+      <c r="E68" s="10" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2033,16 +2041,16 @@
       <c r="A69">
         <v>89</v>
       </c>
-      <c r="B69" s="3">
-        <v>46314</v>
-      </c>
-      <c r="C69" s="5" t="s">
+      <c r="B69" s="12">
+        <v>45949</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D69" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E69" s="6" t="s">
+      <c r="E69" s="10" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2050,31 +2058,31 @@
       <c r="A70">
         <v>90</v>
       </c>
-      <c r="B70" s="3">
-        <v>46315</v>
-      </c>
-      <c r="C70" s="5" t="s">
+      <c r="B70" s="12">
+        <v>45950</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D70" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E70" s="6" t="s">
+      <c r="E70" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>91</v>
       </c>
-      <c r="B71" s="3">
-        <v>46320</v>
-      </c>
-      <c r="C71" s="5" t="s">
+      <c r="B71" s="12">
+        <v>45955</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D71" s="4"/>
-      <c r="E71" s="6" t="s">
+      <c r="D71" s="3"/>
+      <c r="E71" s="10" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2082,14 +2090,14 @@
       <c r="A72">
         <v>94</v>
       </c>
-      <c r="B72" s="3">
-        <v>46327</v>
-      </c>
-      <c r="C72" s="5" t="s">
+      <c r="B72" s="12">
+        <v>45962</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D72" s="4"/>
-      <c r="E72" s="6" t="s">
+      <c r="D72" s="3"/>
+      <c r="E72" s="10" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2097,16 +2105,16 @@
       <c r="A73">
         <v>95</v>
       </c>
-      <c r="B73" s="3">
-        <v>46350</v>
-      </c>
-      <c r="C73" s="5" t="s">
+      <c r="B73" s="12">
+        <v>45985</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="D73" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E73" s="6" t="s">
+      <c r="E73" s="10" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2114,14 +2122,14 @@
       <c r="A74">
         <v>96</v>
       </c>
-      <c r="B74" s="3">
-        <v>46351</v>
-      </c>
-      <c r="C74" s="5" t="s">
+      <c r="B74" s="12">
+        <v>45986</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D74" s="4"/>
-      <c r="E74" s="6" t="s">
+      <c r="D74" s="3"/>
+      <c r="E74" s="10" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2129,14 +2137,14 @@
       <c r="A75">
         <v>97</v>
       </c>
-      <c r="B75" s="3">
-        <v>46351</v>
-      </c>
-      <c r="C75" s="5" t="s">
+      <c r="B75" s="12">
+        <v>45986</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D75" s="4"/>
-      <c r="E75" s="6" t="s">
+      <c r="D75" s="3"/>
+      <c r="E75" s="10" t="s">
         <v>106</v>
       </c>
     </row>
@@ -2144,14 +2152,14 @@
       <c r="A76">
         <v>98</v>
       </c>
-      <c r="B76" s="3">
-        <v>46351</v>
-      </c>
-      <c r="C76" s="5" t="s">
+      <c r="B76" s="12">
+        <v>45986</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D76" s="4"/>
-      <c r="E76" s="6" t="s">
+      <c r="D76" s="3"/>
+      <c r="E76" s="10" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2159,14 +2167,14 @@
       <c r="A77">
         <v>99</v>
       </c>
-      <c r="B77" s="3">
-        <v>46352</v>
-      </c>
-      <c r="C77" s="5" t="s">
+      <c r="B77" s="12">
+        <v>45987</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="6" t="s">
+      <c r="D77" s="3"/>
+      <c r="E77" s="10" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2174,14 +2182,14 @@
       <c r="A78">
         <v>100</v>
       </c>
-      <c r="B78" s="3">
-        <v>46355</v>
-      </c>
-      <c r="C78" s="5" t="s">
+      <c r="B78" s="12">
+        <v>45990</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D78" s="4"/>
-      <c r="E78" s="6" t="s">
+      <c r="D78" s="3"/>
+      <c r="E78" s="10" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2189,14 +2197,14 @@
       <c r="A79">
         <v>101</v>
       </c>
-      <c r="B79" s="3">
-        <v>46355</v>
-      </c>
-      <c r="C79" s="5" t="s">
+      <c r="B79" s="12">
+        <v>45990</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D79" s="4"/>
-      <c r="E79" s="6" t="s">
+      <c r="D79" s="3"/>
+      <c r="E79" s="10" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2204,16 +2212,16 @@
       <c r="A80">
         <v>102</v>
       </c>
-      <c r="B80" s="3">
-        <v>46355</v>
-      </c>
-      <c r="C80" s="5" t="s">
+      <c r="B80" s="12">
+        <v>45990</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="D80" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E80" s="6" t="s">
+      <c r="E80" s="10" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2221,16 +2229,16 @@
       <c r="A81">
         <v>104</v>
       </c>
-      <c r="B81" s="10">
-        <v>46266</v>
-      </c>
-      <c r="C81" s="11" t="s">
+      <c r="B81" s="14">
+        <v>45901</v>
+      </c>
+      <c r="C81" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D81" s="11" t="s">
+      <c r="D81" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="E81" s="12" t="s">
+      <c r="E81" s="11" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2238,14 +2246,14 @@
       <c r="A82">
         <v>106</v>
       </c>
-      <c r="B82" s="3">
-        <v>46366</v>
-      </c>
-      <c r="C82" s="5" t="s">
+      <c r="B82" s="12">
+        <v>46001</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D82" s="4"/>
-      <c r="E82" s="6" t="s">
+      <c r="D82" s="3"/>
+      <c r="E82" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2253,14 +2261,14 @@
       <c r="A83">
         <v>107</v>
       </c>
-      <c r="B83" s="3">
-        <v>46373</v>
-      </c>
-      <c r="C83" s="5" t="s">
+      <c r="B83" s="12">
+        <v>46008</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D83" s="4"/>
-      <c r="E83" s="6" t="s">
+      <c r="D83" s="3"/>
+      <c r="E83" s="10" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2268,14 +2276,14 @@
       <c r="A84">
         <v>109</v>
       </c>
-      <c r="B84" s="3">
-        <v>46387</v>
-      </c>
-      <c r="C84" s="5" t="s">
+      <c r="B84" s="12">
+        <v>46022</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D84" s="4"/>
-      <c r="E84" s="6" t="s">
+      <c r="D84" s="3"/>
+      <c r="E84" s="10" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2283,14 +2291,14 @@
       <c r="A85">
         <v>110</v>
       </c>
-      <c r="B85" s="3">
+      <c r="B85" s="12">
         <v>46023</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="C85" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D85" s="4"/>
-      <c r="E85" s="6" t="s">
+      <c r="D85" s="3"/>
+      <c r="E85" s="10" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2298,14 +2306,14 @@
       <c r="A86">
         <v>111</v>
       </c>
-      <c r="B86" s="3">
+      <c r="B86" s="12">
         <v>46040</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D86" s="4"/>
-      <c r="E86" s="6" t="s">
+      <c r="D86" s="3"/>
+      <c r="E86" s="10" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2313,14 +2321,14 @@
       <c r="A87">
         <v>112</v>
       </c>
-      <c r="B87" s="3">
+      <c r="B87" s="12">
         <v>46023</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="C87" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D87" s="4"/>
-      <c r="E87" s="6" t="s">
+      <c r="D87" s="3"/>
+      <c r="E87" s="10" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2328,14 +2336,14 @@
       <c r="A88">
         <v>113</v>
       </c>
-      <c r="B88" s="3">
+      <c r="B88" s="12">
         <v>46023</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="C88" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D88" s="4"/>
-      <c r="E88" s="6" t="s">
+      <c r="D88" s="3"/>
+      <c r="E88" s="10" t="s">
         <v>106</v>
       </c>
     </row>
@@ -2343,16 +2351,16 @@
       <c r="A89">
         <v>114</v>
       </c>
-      <c r="B89" s="3">
+      <c r="B89" s="12">
         <v>46023</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C89" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="D89" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E89" s="6" t="s">
+      <c r="E89" s="10" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2360,16 +2368,16 @@
       <c r="A90">
         <v>115</v>
       </c>
-      <c r="B90" s="3">
+      <c r="B90" s="12">
         <v>46054</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="C90" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="D90" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E90" s="6" t="s">
+      <c r="E90" s="10" t="s">
         <v>128</v>
       </c>
     </row>
@@ -2377,72 +2385,75 @@
       <c r="A91">
         <v>116</v>
       </c>
-      <c r="B91" s="3">
+      <c r="B91" s="12">
         <v>46082</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="C91" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D91" s="5" t="s">
+      <c r="D91" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="6" t="s">
+      <c r="E91" s="10" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="3">
+      <c r="B92" s="12">
         <v>46096</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="C92" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D92" s="4"/>
-      <c r="E92" s="6" t="s">
+      <c r="D92" s="3"/>
+      <c r="E92" s="10" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="3">
+      <c r="B93" s="12">
         <v>46082</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C93" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D93" s="4"/>
-      <c r="E93" s="6" t="s">
+      <c r="D93" s="3"/>
+      <c r="E93" s="10" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B94" s="3">
+      <c r="B94" s="12">
         <v>46123</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="C94" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D94" s="4"/>
-      <c r="E94" s="6" t="s">
+      <c r="D94" s="3"/>
+      <c r="E94" s="10" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="3">
+      <c r="B95" s="12">
         <v>46143</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="C95" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D95" s="4"/>
-      <c r="E95" s="6" t="s">
+      <c r="D95" s="3"/>
+      <c r="E95" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="7"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="8"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="10">
+        <f>SUM(E2:E95)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
